--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/12.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/12.xlsx
@@ -426,13 +426,13 @@
         <v>-20.03974548973078</v>
       </c>
       <c r="E2">
-        <v>-14.84854229773015</v>
+        <v>-18.18373170506132</v>
       </c>
       <c r="F2">
-        <v>-5.41625032839055</v>
+        <v>-6.147960866192024</v>
       </c>
       <c r="G2">
-        <v>-6.590320708423183</v>
+        <v>-9.532909042640995</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.89932845697044</v>
       </c>
       <c r="E3">
-        <v>-12.43582115965747</v>
+        <v>-17.5852485802076</v>
       </c>
       <c r="F3">
-        <v>-5.445813366714058</v>
+        <v>-5.215179857954527</v>
       </c>
       <c r="G3">
-        <v>-6.288878984344844</v>
+        <v>-10.40475776313576</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.64934623626554</v>
       </c>
       <c r="E4">
-        <v>-14.29692887885582</v>
+        <v>-19.29105681178691</v>
       </c>
       <c r="F4">
-        <v>-5.081724127872276</v>
+        <v>-5.636640427289019</v>
       </c>
       <c r="G4">
-        <v>-6.001606395174587</v>
+        <v>-8.714956003525566</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.29137242242374</v>
       </c>
       <c r="E5">
-        <v>-14.84899514513092</v>
+        <v>-19.41859222526493</v>
       </c>
       <c r="F5">
-        <v>-5.073145984781298</v>
+        <v>-5.740427802604386</v>
       </c>
       <c r="G5">
-        <v>-6.071141093681439</v>
+        <v>-9.277020425183029</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.81867918939737</v>
       </c>
       <c r="E6">
-        <v>-14.60658140302632</v>
+        <v>-20.58941106605207</v>
       </c>
       <c r="F6">
-        <v>-4.566651493729116</v>
+        <v>-5.12899537388927</v>
       </c>
       <c r="G6">
-        <v>-4.723126676636683</v>
+        <v>-9.50004194652711</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.23037033634881</v>
       </c>
       <c r="E7">
-        <v>-17.60595729184468</v>
+        <v>-19.3401726408741</v>
       </c>
       <c r="F7">
-        <v>-4.574916063048836</v>
+        <v>-4.7389404847109</v>
       </c>
       <c r="G7">
-        <v>-4.751703305731672</v>
+        <v>-9.502081242579301</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.53812086604188</v>
       </c>
       <c r="E8">
-        <v>-16.32537276958562</v>
+        <v>-21.46682554740824</v>
       </c>
       <c r="F8">
-        <v>-4.168721626886223</v>
+        <v>-4.402212932970165</v>
       </c>
       <c r="G8">
-        <v>-5.956093015100687</v>
+        <v>-8.541314579445253</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.77089927334176</v>
       </c>
       <c r="E9">
-        <v>-18.70158082173445</v>
+        <v>-20.23177935977031</v>
       </c>
       <c r="F9">
-        <v>-4.062594326080795</v>
+        <v>-4.466023611715051</v>
       </c>
       <c r="G9">
-        <v>-4.716270536824853</v>
+        <v>-8.731551768313933</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.96073468358188</v>
       </c>
       <c r="E10">
-        <v>-20.77925375340163</v>
+        <v>-24.02823912952278</v>
       </c>
       <c r="F10">
-        <v>-4.04224291321444</v>
+        <v>-4.697833813969754</v>
       </c>
       <c r="G10">
-        <v>-4.225283527895543</v>
+        <v>-8.316594748239526</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.13126566133682</v>
       </c>
       <c r="E11">
-        <v>-21.30231514365759</v>
+        <v>-24.88208290366903</v>
       </c>
       <c r="F11">
-        <v>-3.549098271176454</v>
+        <v>-4.36237322696137</v>
       </c>
       <c r="G11">
-        <v>-3.492577036416347</v>
+        <v>-8.303336013354745</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.30958061596405</v>
       </c>
       <c r="E12">
-        <v>-20.36596257309159</v>
+        <v>-24.36669727685606</v>
       </c>
       <c r="F12">
-        <v>-3.311888423603061</v>
+        <v>-4.870411831281106</v>
       </c>
       <c r="G12">
-        <v>-3.325136264131089</v>
+        <v>-7.326149044345911</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.51647344398243</v>
       </c>
       <c r="E13">
-        <v>-23.21535993124992</v>
+        <v>-25.37097242906311</v>
       </c>
       <c r="F13">
-        <v>-3.30118969829131</v>
+        <v>-3.728508395807012</v>
       </c>
       <c r="G13">
-        <v>-3.28738611334678</v>
+        <v>-7.524447411602716</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.79034054763978</v>
       </c>
       <c r="E14">
-        <v>-22.18498265486266</v>
+        <v>-24.03938823252966</v>
       </c>
       <c r="F14">
-        <v>-3.496880319732585</v>
+        <v>-4.258519335997555</v>
       </c>
       <c r="G14">
-        <v>-2.51295350589061</v>
+        <v>-7.148948783810881</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.15031271915568</v>
       </c>
       <c r="E15">
-        <v>-25.1126139299775</v>
+        <v>-27.59529999146869</v>
       </c>
       <c r="F15">
-        <v>-2.91568400435504</v>
+        <v>-3.182436302075041</v>
       </c>
       <c r="G15">
-        <v>-4.023757378737948</v>
+        <v>-4.152699816947022</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.60281918708405</v>
       </c>
       <c r="E16">
-        <v>-23.19500444058544</v>
+        <v>-27.99470687047121</v>
       </c>
       <c r="F16">
-        <v>-3.001695864475514</v>
+        <v>-3.393034347298348</v>
       </c>
       <c r="G16">
-        <v>-1.918233863033777</v>
+        <v>-5.702518468974671</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.15653141614896</v>
       </c>
       <c r="E17">
-        <v>-25.26464838783702</v>
+        <v>-28.61346397345726</v>
       </c>
       <c r="F17">
-        <v>-2.550079158952181</v>
+        <v>-3.411610425833494</v>
       </c>
       <c r="G17">
-        <v>-2.048937511469743</v>
+        <v>-5.449890738872886</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.81668833296995</v>
       </c>
       <c r="E18">
-        <v>-26.16246817307175</v>
+        <v>-28.79727020495459</v>
       </c>
       <c r="F18">
-        <v>-2.896721501576525</v>
+        <v>-3.626267509318073</v>
       </c>
       <c r="G18">
-        <v>-3.017298566070879</v>
+        <v>-6.359853770161279</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.58645053629115</v>
       </c>
       <c r="E19">
-        <v>-27.19882756362314</v>
+        <v>-29.28176258208723</v>
       </c>
       <c r="F19">
-        <v>-2.660122172633534</v>
+        <v>-2.766083184317841</v>
       </c>
       <c r="G19">
-        <v>-3.990949872443771</v>
+        <v>-3.783388598768085</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.45227201245083</v>
       </c>
       <c r="E20">
-        <v>-28.77583240900228</v>
+        <v>-30.19797929297812</v>
       </c>
       <c r="F20">
-        <v>-1.686176292462498</v>
+        <v>-2.327476622889844</v>
       </c>
       <c r="G20">
-        <v>-1.070664683524029</v>
+        <v>-4.217424292785313</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.39714762751093</v>
       </c>
       <c r="E21">
-        <v>-26.97951809590568</v>
+        <v>-30.23887367750439</v>
       </c>
       <c r="F21">
-        <v>-1.366815659790471</v>
+        <v>-3.041833307196411</v>
       </c>
       <c r="G21">
-        <v>-1.234354607713292</v>
+        <v>-5.932270329400091</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.40394638477806</v>
       </c>
       <c r="E22">
-        <v>-28.02160600607677</v>
+        <v>-31.5824787082912</v>
       </c>
       <c r="F22">
-        <v>-1.359509232549591</v>
+        <v>-1.902206448975762</v>
       </c>
       <c r="G22">
-        <v>-0.2694596942917729</v>
+        <v>-5.526480209923926</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.46580156767078</v>
       </c>
       <c r="E23">
-        <v>-30.05295944135649</v>
+        <v>-32.70411605711804</v>
       </c>
       <c r="F23">
-        <v>-0.7559074377333662</v>
+        <v>-1.702693553307573</v>
       </c>
       <c r="G23">
-        <v>-2.503203949277457</v>
+        <v>-4.548028612519091</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.56782550449182</v>
       </c>
       <c r="E24">
-        <v>-29.11285050160113</v>
+        <v>-30.7448378141444</v>
       </c>
       <c r="F24">
-        <v>-0.4729364077333498</v>
+        <v>-1.889674584066889</v>
       </c>
       <c r="G24">
-        <v>-2.716512330009317</v>
+        <v>-3.888054806537683</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.68693948745771</v>
       </c>
       <c r="E25">
-        <v>-28.8119152898954</v>
+        <v>-33.34613593108149</v>
       </c>
       <c r="F25">
-        <v>-1.006210573962655</v>
+        <v>-1.552633458554897</v>
       </c>
       <c r="G25">
-        <v>-2.477216166794178</v>
+        <v>-4.798673325842851</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.8098302302521</v>
       </c>
       <c r="E26">
-        <v>-28.67095747945864</v>
+        <v>-32.88990123175672</v>
       </c>
       <c r="F26">
-        <v>-0.0382621880933887</v>
+        <v>-1.403608315617961</v>
       </c>
       <c r="G26">
-        <v>-2.430428226687658</v>
+        <v>-7.534812729686173</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.92555377149617</v>
       </c>
       <c r="E27">
-        <v>-29.89543873723668</v>
+        <v>-31.77103530902258</v>
       </c>
       <c r="F27">
-        <v>0.08140975755383542</v>
+        <v>-1.324114989045435</v>
       </c>
       <c r="G27">
-        <v>-2.711563064428106</v>
+        <v>-6.1549905911001</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.03215147252199</v>
       </c>
       <c r="E28">
-        <v>-31.1024966912702</v>
+        <v>-31.65952163658369</v>
       </c>
       <c r="F28">
-        <v>-0.2144241318913802</v>
+        <v>-2.425945121888207</v>
       </c>
       <c r="G28">
-        <v>-1.414001361401843</v>
+        <v>-6.200444381354293</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.12177381075357</v>
       </c>
       <c r="E29">
-        <v>-29.51226190907765</v>
+        <v>-32.16903609684571</v>
       </c>
       <c r="F29">
-        <v>-0.108113121199761</v>
+        <v>-1.094287586596863</v>
       </c>
       <c r="G29">
-        <v>-2.516161424518164</v>
+        <v>-6.004983151624644</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.18591785396578</v>
       </c>
       <c r="E30">
-        <v>-28.75059975183154</v>
+        <v>-31.67779402920464</v>
       </c>
       <c r="F30">
-        <v>-0.5106135633146119</v>
+        <v>-2.199066579854182</v>
       </c>
       <c r="G30">
-        <v>-1.453860329694668</v>
+        <v>-5.210571401838973</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.22449841523304</v>
       </c>
       <c r="E31">
-        <v>-31.9001081394262</v>
+        <v>-27.98935421419414</v>
       </c>
       <c r="F31">
-        <v>-0.04703116774717692</v>
+        <v>-1.760944632436309</v>
       </c>
       <c r="G31">
-        <v>-1.271829983217842</v>
+        <v>-6.731753834951926</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.24332400909271</v>
       </c>
       <c r="E32">
-        <v>-28.07433555742208</v>
+        <v>-31.51584674174234</v>
       </c>
       <c r="F32">
-        <v>-0.5736228868662858</v>
+        <v>-1.056041880591958</v>
       </c>
       <c r="G32">
-        <v>-2.804218612981229</v>
+        <v>-6.995806257709735</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.24747925473228</v>
       </c>
       <c r="E33">
-        <v>-28.46348091432322</v>
+        <v>-30.49326523335928</v>
       </c>
       <c r="F33">
-        <v>0.2922999965185408</v>
+        <v>-1.200319073194407</v>
       </c>
       <c r="G33">
-        <v>-3.695308224150236</v>
+        <v>-6.316419412686042</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.23465961226839</v>
       </c>
       <c r="E34">
-        <v>-28.54694069028458</v>
+        <v>-32.0409119817467</v>
       </c>
       <c r="F34">
-        <v>-0.2803807321516869</v>
+        <v>-1.999308209769101</v>
       </c>
       <c r="G34">
-        <v>-2.998792616506353</v>
+        <v>-5.445590340217374</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.20729397337847</v>
       </c>
       <c r="E35">
-        <v>-27.6951981280779</v>
+        <v>-28.01750773709983</v>
       </c>
       <c r="F35">
-        <v>-0.3629092311111519</v>
+        <v>-1.367878326459731</v>
       </c>
       <c r="G35">
-        <v>-2.003867744498105</v>
+        <v>-3.59890182750112</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.16688702301212</v>
       </c>
       <c r="E36">
-        <v>-29.27778205343449</v>
+        <v>-28.78471274653132</v>
       </c>
       <c r="F36">
-        <v>-0.08648603321851987</v>
+        <v>-1.592568978771576</v>
       </c>
       <c r="G36">
-        <v>-1.781799660269333</v>
+        <v>-5.603380872255656</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.1239036483272</v>
       </c>
       <c r="E37">
-        <v>-26.37539702091241</v>
+        <v>-25.97372137643205</v>
       </c>
       <c r="F37">
-        <v>-0.7297905434818543</v>
+        <v>-1.505689247809441</v>
       </c>
       <c r="G37">
-        <v>-2.670389809556191</v>
+        <v>-5.449685485049452</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.07996587274</v>
       </c>
       <c r="E38">
-        <v>-26.95891353917077</v>
+        <v>-29.64004186015208</v>
       </c>
       <c r="F38">
-        <v>-0.6807162482801321</v>
+        <v>-1.048559661994464</v>
       </c>
       <c r="G38">
-        <v>-2.384024309863694</v>
+        <v>-6.452880099814799</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.02952185843381</v>
       </c>
       <c r="E39">
-        <v>-25.68654366876163</v>
+        <v>-26.85792404032572</v>
       </c>
       <c r="F39">
-        <v>-0.01370128490379603</v>
+        <v>-1.589085617610567</v>
       </c>
       <c r="G39">
-        <v>-1.459875590939524</v>
+        <v>-5.935398794934702</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.97603790181081</v>
       </c>
       <c r="E40">
-        <v>-25.24054784916819</v>
+        <v>-27.41812797439259</v>
       </c>
       <c r="F40">
-        <v>-0.8951436944069716</v>
+        <v>-1.578921393045277</v>
       </c>
       <c r="G40">
-        <v>-1.328950135952427</v>
+        <v>-5.993022150591257</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.92419620549073</v>
       </c>
       <c r="E41">
-        <v>-26.96337861454234</v>
+        <v>-27.69169761766997</v>
       </c>
       <c r="F41">
-        <v>0.03208840422930472</v>
+        <v>-2.335733273679987</v>
       </c>
       <c r="G41">
-        <v>-1.936865613328795</v>
+        <v>-5.63120931805877</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.88117387130127</v>
       </c>
       <c r="E42">
-        <v>-23.00379415408557</v>
+        <v>-25.72745390294692</v>
       </c>
       <c r="F42">
-        <v>-0.2221161915226696</v>
+        <v>-1.726609096336625</v>
       </c>
       <c r="G42">
-        <v>-1.629213305818785</v>
+        <v>-4.6288390291327</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.84603973385617</v>
       </c>
       <c r="E43">
-        <v>-24.82547697857315</v>
+        <v>-25.99242397408373</v>
       </c>
       <c r="F43">
-        <v>-0.9607922638667252</v>
+        <v>-1.617488591351016</v>
       </c>
       <c r="G43">
-        <v>-1.559251546937367</v>
+        <v>-5.759900154806859</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.81929546646242</v>
       </c>
       <c r="E44">
-        <v>-22.83796143592468</v>
+        <v>-26.93028452649428</v>
       </c>
       <c r="F44">
-        <v>-0.565039200804604</v>
+        <v>-1.316560711828789</v>
       </c>
       <c r="G44">
-        <v>-2.009300349728049</v>
+        <v>-4.522497685320231</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.80388539485955</v>
       </c>
       <c r="E45">
-        <v>-22.36907418022248</v>
+        <v>-22.31510382699906</v>
       </c>
       <c r="F45">
-        <v>-0.3289308206953986</v>
+        <v>-1.538103748633698</v>
       </c>
       <c r="G45">
-        <v>-1.115383532668504</v>
+        <v>-4.582044467935102</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.81153011778648</v>
       </c>
       <c r="E46">
-        <v>-23.43225119384729</v>
+        <v>-23.71293959826472</v>
       </c>
       <c r="F46">
-        <v>-0.8878507286663729</v>
+        <v>-1.601226307158326</v>
       </c>
       <c r="G46">
-        <v>-1.103055061080258</v>
+        <v>-5.300869841968134</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.84727663304118</v>
       </c>
       <c r="E47">
-        <v>-20.94379132799632</v>
+        <v>-24.22991019098037</v>
       </c>
       <c r="F47">
-        <v>-1.336985767020212</v>
+        <v>-1.431312083196743</v>
       </c>
       <c r="G47">
-        <v>-0.7451089457376393</v>
+        <v>-6.086108070064484</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.90570571819389</v>
       </c>
       <c r="E48">
-        <v>-19.91580055741111</v>
+        <v>-20.98820660106355</v>
       </c>
       <c r="F48">
-        <v>-1.405243491975652</v>
+        <v>-1.682228113615307</v>
       </c>
       <c r="G48">
-        <v>-1.559774613132572</v>
+        <v>-5.89875436636051</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.99023622386731</v>
       </c>
       <c r="E49">
-        <v>-18.05526795441173</v>
+        <v>-24.11969619058169</v>
       </c>
       <c r="F49">
-        <v>-0.4965755940801567</v>
+        <v>-2.752131527055777</v>
       </c>
       <c r="G49">
-        <v>-0.1921485243131729</v>
+        <v>-4.382438435190285</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.10198512321763</v>
       </c>
       <c r="E50">
-        <v>-19.28295537178719</v>
+        <v>-25.32520767074159</v>
       </c>
       <c r="F50">
-        <v>-1.217609974379175</v>
+        <v>-1.751583346770147</v>
       </c>
       <c r="G50">
-        <v>-2.151710087190878</v>
+        <v>-4.683952991270487</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.24568185765775</v>
       </c>
       <c r="E51">
-        <v>-19.66309812236108</v>
+        <v>-22.49996519294018</v>
       </c>
       <c r="F51">
-        <v>-1.152382670692928</v>
+        <v>-2.15347168654868</v>
       </c>
       <c r="G51">
-        <v>-0.5823492848449107</v>
+        <v>-7.051320795857774</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.41542531837618</v>
       </c>
       <c r="E52">
-        <v>-19.56861151219103</v>
+        <v>-21.52531984616532</v>
       </c>
       <c r="F52">
-        <v>-1.249182735509375</v>
+        <v>-2.638819744364957</v>
       </c>
       <c r="G52">
-        <v>-0.1156517485372336</v>
+        <v>-5.51964393338533</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.60038474280613</v>
       </c>
       <c r="E53">
-        <v>-18.20643747373578</v>
+        <v>-19.65084860017033</v>
       </c>
       <c r="F53">
-        <v>-1.267115037589896</v>
+        <v>-2.246455020108919</v>
       </c>
       <c r="G53">
-        <v>-2.029186796782451</v>
+        <v>-4.602043473537839</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.79533518083626</v>
       </c>
       <c r="E54">
-        <v>-18.1874405252736</v>
+        <v>-21.4254171810821</v>
       </c>
       <c r="F54">
-        <v>-0.8890543451621069</v>
+        <v>-2.030161176560734</v>
       </c>
       <c r="G54">
-        <v>-1.216222749794704</v>
+        <v>-5.609161084767224</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.9988898305105</v>
       </c>
       <c r="E55">
-        <v>-18.4001565348359</v>
+        <v>-21.70421721183834</v>
       </c>
       <c r="F55">
-        <v>-1.537570039740195</v>
+        <v>-2.606047326003811</v>
       </c>
       <c r="G55">
-        <v>-1.769964459966438</v>
+        <v>-4.159559267304392</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.20671283055887</v>
       </c>
       <c r="E56">
-        <v>-16.49305310514163</v>
+        <v>-21.11448762724145</v>
       </c>
       <c r="F56">
-        <v>-2.160151758100004</v>
+        <v>-2.3454382235298</v>
       </c>
       <c r="G56">
-        <v>-1.029521223561966</v>
+        <v>-5.938696098291817</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.40529230980972</v>
       </c>
       <c r="E57">
-        <v>-16.09079781598829</v>
+        <v>-20.23789279968067</v>
       </c>
       <c r="F57">
-        <v>-2.011708627086992</v>
+        <v>-2.196832762660455</v>
       </c>
       <c r="G57">
-        <v>-1.599994430889177</v>
+        <v>-6.009392798282953</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.58865442608468</v>
       </c>
       <c r="E58">
-        <v>-16.97379137732191</v>
+        <v>-20.14214727373649</v>
       </c>
       <c r="F58">
-        <v>-1.834226664408481</v>
+        <v>-2.539125456988044</v>
       </c>
       <c r="G58">
-        <v>-1.01406097589357</v>
+        <v>-4.990992847855733</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.75172262615047</v>
       </c>
       <c r="E59">
-        <v>-13.00310762707234</v>
+        <v>-20.04748405308015</v>
       </c>
       <c r="F59">
-        <v>-1.024671041965975</v>
+        <v>-2.642415548645963</v>
       </c>
       <c r="G59">
-        <v>-2.828984804160516</v>
+        <v>-3.879794995417202</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.89918480194099</v>
       </c>
       <c r="E60">
-        <v>-15.03210399163107</v>
+        <v>-19.90480542252048</v>
       </c>
       <c r="F60">
-        <v>-1.3835435535223</v>
+        <v>-3.120188741068693</v>
       </c>
       <c r="G60">
-        <v>-1.990165396511062</v>
+        <v>-4.809018780653074</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.02819567155236</v>
       </c>
       <c r="E61">
-        <v>-15.26897941002429</v>
+        <v>-18.81092988359767</v>
       </c>
       <c r="F61">
-        <v>-1.076755962112948</v>
+        <v>-2.329632838493714</v>
       </c>
       <c r="G61">
-        <v>-1.588477042958053</v>
+        <v>-7.655449009137215</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.1299197272734</v>
       </c>
       <c r="E62">
-        <v>-14.23646469390541</v>
+        <v>-19.67658391795592</v>
       </c>
       <c r="F62">
-        <v>-1.692295732119756</v>
+        <v>-2.218859736385344</v>
       </c>
       <c r="G62">
-        <v>-1.703905834275821</v>
+        <v>-6.517147720368671</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.20663357071938</v>
       </c>
       <c r="E63">
-        <v>-14.93285795527897</v>
+        <v>-19.63348643082492</v>
       </c>
       <c r="F63">
-        <v>-1.823895358869112</v>
+        <v>-2.617488809389904</v>
       </c>
       <c r="G63">
-        <v>-2.636360711958022</v>
+        <v>-7.524175946868495</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.26257736070149</v>
       </c>
       <c r="E64">
-        <v>-14.96114280393087</v>
+        <v>-18.3080020887798</v>
       </c>
       <c r="F64">
-        <v>-2.101593440023673</v>
+        <v>-3.520369845870383</v>
       </c>
       <c r="G64">
-        <v>-3.121140448001198</v>
+        <v>-7.712337423684051</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.30312567636817</v>
       </c>
       <c r="E65">
-        <v>-13.94087308152874</v>
+        <v>-15.48783150186698</v>
       </c>
       <c r="F65">
-        <v>-2.258944124958075</v>
+        <v>-3.430884126824393</v>
       </c>
       <c r="G65">
-        <v>-3.031788823896269</v>
+        <v>-6.87086957960318</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.32450095890159</v>
       </c>
       <c r="E66">
-        <v>-15.08603358858842</v>
+        <v>-17.17322537261972</v>
       </c>
       <c r="F66">
-        <v>-2.035397700170135</v>
+        <v>-2.237298032505848</v>
       </c>
       <c r="G66">
-        <v>-2.208118472634519</v>
+        <v>-6.245236062500632</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.32499281987566</v>
       </c>
       <c r="E67">
-        <v>-14.22633449755025</v>
+        <v>-15.28974699182347</v>
       </c>
       <c r="F67">
-        <v>-2.300584504592724</v>
+        <v>-3.228373275858277</v>
       </c>
       <c r="G67">
-        <v>-4.253313916976552</v>
+        <v>-6.753262449320571</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.30341213159165</v>
       </c>
       <c r="E68">
-        <v>-14.02439625612621</v>
+        <v>-17.8807949078442</v>
       </c>
       <c r="F68">
-        <v>-2.291463942225708</v>
+        <v>-2.957870762530515</v>
       </c>
       <c r="G68">
-        <v>-3.634526608049217</v>
+        <v>-6.706414919394344</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.26859578164415</v>
       </c>
       <c r="E69">
-        <v>-13.53704641189473</v>
+        <v>-17.10084224408111</v>
       </c>
       <c r="F69">
-        <v>-1.94139208444148</v>
+        <v>-2.875371562130486</v>
       </c>
       <c r="G69">
-        <v>-2.652711496376483</v>
+        <v>-6.999613385079897</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.22147309032084</v>
       </c>
       <c r="E70">
-        <v>-14.51714856984884</v>
+        <v>-20.0413706131698</v>
       </c>
       <c r="F70">
-        <v>-2.02109921131259</v>
+        <v>-3.075560700224567</v>
       </c>
       <c r="G70">
-        <v>-4.186589871632541</v>
+        <v>-5.710847801551477</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.15357905721931</v>
       </c>
       <c r="E71">
-        <v>-12.80680733578785</v>
+        <v>-18.82951474092515</v>
       </c>
       <c r="F71">
-        <v>-2.414291421909446</v>
+        <v>-2.750744200673852</v>
       </c>
       <c r="G71">
-        <v>-5.194313312695612</v>
+        <v>-8.69989964241296</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.06647610681717</v>
       </c>
       <c r="E72">
-        <v>-13.38134841856301</v>
+        <v>-19.87590470140353</v>
       </c>
       <c r="F72">
-        <v>-2.667238555164561</v>
+        <v>-2.677942031594058</v>
       </c>
       <c r="G72">
-        <v>-5.11841905620782</v>
+        <v>-8.337524017138797</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.96103849354392</v>
       </c>
       <c r="E73">
-        <v>-14.06975798026104</v>
+        <v>-17.19013016609035</v>
       </c>
       <c r="F73">
-        <v>-2.618541973823671</v>
+        <v>-2.908588210000913</v>
       </c>
       <c r="G73">
-        <v>-4.584739252004069</v>
+        <v>-8.548419010172529</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.84361175961817</v>
       </c>
       <c r="E74">
-        <v>-14.86617164704201</v>
+        <v>-17.4426695760761</v>
       </c>
       <c r="F74">
-        <v>-2.527127300972675</v>
+        <v>-3.193505614571004</v>
       </c>
       <c r="G74">
-        <v>-3.986268761051242</v>
+        <v>-8.935590621535834</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.71130422784037</v>
       </c>
       <c r="E75">
-        <v>-14.1644302578654</v>
+        <v>-18.81803958778971</v>
       </c>
       <c r="F75">
-        <v>-2.212472650428377</v>
+        <v>-3.669032320152684</v>
       </c>
       <c r="G75">
-        <v>-5.489974824262382</v>
+        <v>-8.661695946889772</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.55952729305913</v>
       </c>
       <c r="E76">
-        <v>-13.39231185413558</v>
+        <v>-19.13269607573868</v>
       </c>
       <c r="F76">
-        <v>-2.381169004540987</v>
+        <v>-3.143966501683101</v>
       </c>
       <c r="G76">
-        <v>-5.59232696070003</v>
+        <v>-6.486713875226151</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.38740285595741</v>
       </c>
       <c r="E77">
-        <v>-16.27713546445591</v>
+        <v>-18.46044410930001</v>
       </c>
       <c r="F77">
-        <v>-2.674942492590216</v>
+        <v>-2.975989150056101</v>
       </c>
       <c r="G77">
-        <v>-4.873302953934642</v>
+        <v>-6.442968326470222</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.20227123419823</v>
       </c>
       <c r="E78">
-        <v>-13.78093643652583</v>
+        <v>-18.34648053242298</v>
       </c>
       <c r="F78">
-        <v>-2.824543312627415</v>
+        <v>-4.101195574063715</v>
       </c>
       <c r="G78">
-        <v>-5.334975082113705</v>
+        <v>-8.454412759039384</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.00746131254869</v>
       </c>
       <c r="E79">
-        <v>-16.07692257162879</v>
+        <v>-18.01204367000851</v>
       </c>
       <c r="F79">
-        <v>-3.253313476614617</v>
+        <v>-3.535101478295801</v>
       </c>
       <c r="G79">
-        <v>-4.32118672162269</v>
+        <v>-7.006525804165896</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.79857130236341</v>
       </c>
       <c r="E80">
-        <v>-15.00685774903831</v>
+        <v>-18.31625296842178</v>
       </c>
       <c r="F80">
-        <v>-2.86981750548504</v>
+        <v>-2.818260751260866</v>
       </c>
       <c r="G80">
-        <v>-4.687776671368345</v>
+        <v>-7.365004917340336</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.57701394960288</v>
       </c>
       <c r="E81">
-        <v>-16.29197527377905</v>
+        <v>-20.77257878271432</v>
       </c>
       <c r="F81">
-        <v>-2.825925096038636</v>
+        <v>-3.335417542388745</v>
       </c>
       <c r="G81">
-        <v>-3.982272932585341</v>
+        <v>-5.798170061240834</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.34360940530577</v>
       </c>
       <c r="E82">
-        <v>-16.36679924980778</v>
+        <v>-22.18221575724397</v>
       </c>
       <c r="F82">
-        <v>-3.062164923738822</v>
+        <v>-3.902819779242813</v>
       </c>
       <c r="G82">
-        <v>-4.923543793038621</v>
+        <v>-7.336759342799275</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.10920348181115</v>
       </c>
       <c r="E83">
-        <v>-16.32520521604733</v>
+        <v>-22.3931747188913</v>
       </c>
       <c r="F83">
-        <v>-3.324298343156444</v>
+        <v>-3.217748192871594</v>
       </c>
       <c r="G83">
-        <v>-5.624882865533222</v>
+        <v>-7.725145924375492</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.87550666225781</v>
       </c>
       <c r="E84">
-        <v>-17.05084789103643</v>
+        <v>-21.2056729798599</v>
       </c>
       <c r="F84">
-        <v>-2.609712021492138</v>
+        <v>-4.398237039269454</v>
       </c>
       <c r="G84">
-        <v>-3.934670598276161</v>
+        <v>-7.455260320377487</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.63986418938267</v>
       </c>
       <c r="E85">
-        <v>-17.31311446319066</v>
+        <v>-22.12773368645769</v>
       </c>
       <c r="F85">
-        <v>-2.86815065500904</v>
+        <v>-3.277027888992408</v>
       </c>
       <c r="G85">
-        <v>-4.478503845648857</v>
+        <v>-7.223061966798545</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.4052051112684</v>
       </c>
       <c r="E86">
-        <v>-20.62946994712392</v>
+        <v>-25.35353780413358</v>
       </c>
       <c r="F86">
-        <v>-2.672204265062421</v>
+        <v>-3.99536600997039</v>
       </c>
       <c r="G86">
-        <v>-3.460156863950264</v>
+        <v>-8.396971483387491</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.17885824885165</v>
       </c>
       <c r="E87">
-        <v>-22.59319288733609</v>
+        <v>-23.02821621440894</v>
       </c>
       <c r="F87">
-        <v>-3.290445837360969</v>
+        <v>-4.232235360771964</v>
       </c>
       <c r="G87">
-        <v>-5.412600753918536</v>
+        <v>-7.671131063356743</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.967973466310291</v>
       </c>
       <c r="E88">
-        <v>-20.25941663663912</v>
+        <v>-24.74984240569703</v>
       </c>
       <c r="F88">
-        <v>-2.961761136111793</v>
+        <v>-3.533150352607979</v>
       </c>
       <c r="G88">
-        <v>-5.334107719182416</v>
+        <v>-6.027971579849343</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.771619883170667</v>
       </c>
       <c r="E89">
-        <v>-23.85775114008201</v>
+        <v>-26.13053790284367</v>
       </c>
       <c r="F89">
-        <v>-2.445514184032334</v>
+        <v>-4.025596580337256</v>
       </c>
       <c r="G89">
-        <v>-4.509834848632519</v>
+        <v>-6.934749866328957</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.590991645945566</v>
       </c>
       <c r="E90">
-        <v>-23.51385429546551</v>
+        <v>-27.85006741066622</v>
       </c>
       <c r="F90">
-        <v>-2.979053621002476</v>
+        <v>-3.690566761337872</v>
       </c>
       <c r="G90">
-        <v>-4.561591917593485</v>
+        <v>-7.042627303271647</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.426200072221498</v>
       </c>
       <c r="E91">
-        <v>-25.40516240782102</v>
+        <v>-29.56390915513513</v>
       </c>
       <c r="F91">
-        <v>-3.133026261219245</v>
+        <v>-3.643654224710724</v>
       </c>
       <c r="G91">
-        <v>-4.938610085787845</v>
+        <v>-7.99497193855379</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.287897143837146</v>
       </c>
       <c r="E92">
-        <v>-29.36744131031235</v>
+        <v>-30.41734083814668</v>
       </c>
       <c r="F92">
-        <v>-3.065590479633918</v>
+        <v>-3.740550895588014</v>
       </c>
       <c r="G92">
-        <v>-4.722838659174767</v>
+        <v>-7.660232747441462</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.17765415533577</v>
       </c>
       <c r="E93">
-        <v>-30.50829976706475</v>
+        <v>-35.15670135188024</v>
       </c>
       <c r="F93">
-        <v>-2.993767832662824</v>
+        <v>-4.011191983183377</v>
       </c>
       <c r="G93">
-        <v>-5.545416530408557</v>
+        <v>-6.173897116674878</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.088806487591274</v>
       </c>
       <c r="E94">
-        <v>-31.5286962867391</v>
+        <v>-32.32422690108857</v>
       </c>
       <c r="F94">
-        <v>-2.8035600011008</v>
+        <v>-3.458122284864035</v>
       </c>
       <c r="G94">
-        <v>-4.436913462038993</v>
+        <v>-8.075467853341168</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.021243347165939</v>
       </c>
       <c r="E95">
-        <v>-34.64023115554244</v>
+        <v>-38.55663208786206</v>
       </c>
       <c r="F95">
-        <v>-2.446869044442992</v>
+        <v>-3.254363473636554</v>
       </c>
       <c r="G95">
-        <v>-3.806290952808764</v>
+        <v>-8.035003055214657</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.974348220006711</v>
       </c>
       <c r="E96">
-        <v>-36.23240638884727</v>
+        <v>-38.34260055660054</v>
       </c>
       <c r="F96">
-        <v>-1.975042667732738</v>
+        <v>-2.672365011212838</v>
       </c>
       <c r="G96">
-        <v>-4.265513277288767</v>
+        <v>-7.417155941220475</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.948419212419235</v>
       </c>
       <c r="E97">
-        <v>-40.68448730424524</v>
+        <v>-39.9774204296356</v>
       </c>
       <c r="F97">
-        <v>-2.083483762880623</v>
+        <v>-3.764715872298747</v>
       </c>
       <c r="G97">
-        <v>-5.872965216609587</v>
+        <v>-7.098721186889058</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.938306397413271</v>
       </c>
       <c r="E98">
-        <v>-41.09641314964196</v>
+        <v>-42.64580336052232</v>
       </c>
       <c r="F98">
-        <v>-1.392650654389035</v>
+        <v>-3.838117474067534</v>
       </c>
       <c r="G98">
-        <v>-5.111271588388534</v>
+        <v>-7.45801469426616</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.933437257235051</v>
       </c>
       <c r="E99">
-        <v>-40.04590907052761</v>
+        <v>-44.54454722719843</v>
       </c>
       <c r="F99">
-        <v>-2.085753213457447</v>
+        <v>-4.434492818791609</v>
       </c>
       <c r="G99">
-        <v>-4.371202443629999</v>
+        <v>-8.181620496057899</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.932215604783604</v>
       </c>
       <c r="E100">
-        <v>-47.52940935682221</v>
+        <v>-46.50899245901482</v>
       </c>
       <c r="F100">
-        <v>-1.745763227530907</v>
+        <v>-3.220215606687848</v>
       </c>
       <c r="G100">
-        <v>-5.914317240940623</v>
+        <v>-6.984957599977544</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.928776565436275</v>
       </c>
       <c r="E101">
-        <v>-46.94459090228664</v>
+        <v>-48.80760510904222</v>
       </c>
       <c r="F101">
-        <v>-1.315477456982628</v>
+        <v>-4.028002229622809</v>
       </c>
       <c r="G101">
-        <v>-6.134872405857949</v>
+        <v>-8.192634681067055</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.931070457912584</v>
       </c>
       <c r="E102">
-        <v>-50.79552255375887</v>
+        <v>-50.5459821256847</v>
       </c>
       <c r="F102">
-        <v>-0.7416588356121575</v>
+        <v>-2.639166575960439</v>
       </c>
       <c r="G102">
-        <v>-5.999573720213474</v>
+        <v>-10.00773396824758</v>
       </c>
     </row>
   </sheetData>
